--- a/technology_surveys/030_email_service_provider_survey--technology_surveys.xlsx
+++ b/technology_surveys/030_email_service_provider_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_page_1</t>
+          <t>email_service_selection</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form</t>
+          <t>Email Service Selection</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_2</t>
+          <t>service_satisfaction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_comments</t>
+          <t>Service Satisfaction</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,69 +561,69 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_3</t>
+          <t>feature_preferences</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_email_service</t>
+          <t>Feature Preferences</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_4</t>
+          <t>pain_points</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_feature_preferences</t>
+          <t>Pain Points</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_5</t>
+          <t>reasons_for_choosing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_satisfaction</t>
+          <t>Reasons for Choosing</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_6</t>
+          <t>feature_comparison</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_feature_painpoints</t>
+          <t>Feature Comparison</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,41 +658,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_7</t>
+          <t>satisfaction_breakdown</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_why_did_you_choose_your_current_email_service</t>
+          <t>Satisfaction Breakdown</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_8</t>
+          <t>ideal_email_service</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_what_is_your_primary_email_service</t>
+          <t>Ideal Email Service</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_9</t>
+          <t>service_comparison</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_comments</t>
+          <t>Service Comparison</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,41 +727,41 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_10</t>
+          <t>pain_points_breakdown</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_additional_comments</t>
+          <t>Pain Points Breakdown</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_11</t>
+          <t>feature_prioritization</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_is_this_survey_understood</t>
+          <t>Feature Prioritization</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,41 +773,41 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_12</t>
+          <t>form_completion_confirmation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_is_form_completed</t>
+          <t>Form Completion Confirmation</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_13</t>
+          <t>current_email_service</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_is_survey_understood</t>
+          <t>Current Email Service</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,18 +819,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_14</t>
+          <t>ideal_email_service_feature</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_is_form_completed</t>
+          <t>Ideal Email Service Feature</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,18 +842,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_15</t>
+          <t>reasons_for_changing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_is_form_understood</t>
+          <t>Reasons for Changing</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,41 +865,41 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_16</t>
+          <t>satisfaction_breakdown_feature</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_is_survey_completed</t>
+          <t>Satisfaction Breakdown Feature</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_17</t>
+          <t>reasons_for_staying</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_what_is_your_current_email_service</t>
+          <t>Reasons for Staying</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,179 +911,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_18</t>
+          <t>feature_comparison_breakdown</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_why_did_you_choose_your_current_email_service</t>
+          <t>Feature Comparison Breakdown</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>email_service_provider_survey_form_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>email_service_provider_survey_what_is_your_reasons_for_choosing_your_current_email_service</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>email_service_provider_survey_form_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>email_service_provider_survey_feature_preferences</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>email_service_provider_survey_form_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>email_service_provider_survey_feature_preferences_2</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>email_service_provider_survey_form_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>email_service_provider_survey_feature_preferences_3</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>email_service_provider_survey_form_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>email_service_provider_survey_satisfaction</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>email_service_provider_survey_form_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>email_service_provider_survey_painpoints</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>email_service_provider_survey_form_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>email_service_provider_survey_what_is_your_ideal_email_service</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,10 +937,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,194 +965,194 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_3_choices</t>
+          <t>email_service_selection_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>gmail</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Gmail</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_3_choices</t>
+          <t>email_service_selection_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>outlook</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Outlook</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_4_choices</t>
+          <t>email_service_selection_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>office_365</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Office 365</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_4_choices</t>
+          <t>email_service_selection_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yahoo</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_8_choices</t>
+          <t>email_service_selection_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>hotmail</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Hotmail</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_8_choices</t>
+          <t>feature_preferences_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_17_choices</t>
+          <t>feature_preferences_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>gmail</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gmail</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_17_choices</t>
+          <t>reasons_for_choosing_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>outlook</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Outlook</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_17_choices</t>
+          <t>reasons_for_choosing_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>office_365</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Office 365</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_17_choices</t>
+          <t>feature_prioritization_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yahoo</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_17_choices</t>
+          <t>feature_prioritization_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hotmail</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hotmail</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_20_choices</t>
+          <t>current_email_service_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1169,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>email_service_provider_survey_form_page_20_choices</t>
+          <t>current_email_service_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1339,74 +1178,6 @@
         </is>
       </c>
       <c r="C14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>email_service_provider_survey_form_page_21_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>email_service_provider_survey_form_page_21_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>email_service_provider_survey_form_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>email_service_provider_survey_form_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
